--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -32733,6 +32733,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1408">
+      <c r="A1408" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1408" t="n">
+        <v>11665</v>
+      </c>
+      <c r="C1408" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>23.0499992370605</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>23.0499992370605</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G1408" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -32756,6 +32756,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1409">
+      <c r="A1409" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1409" t="n">
+        <v>52230</v>
+      </c>
+      <c r="C1409" t="n">
+        <v>23.4500007629395</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>23.4500007629395</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G1409" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -32779,6 +32779,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1410">
+      <c r="A1410" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1410" t="n">
+        <v>11955</v>
+      </c>
+      <c r="C1410" t="n">
+        <v>23.8500003814697</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -32802,6 +32802,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1411">
+      <c r="A1411" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1411" t="n">
+        <v>17320</v>
+      </c>
+      <c r="C1411" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="G1411" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -32643,22 +32643,22 @@
     </row>
     <row r="1404">
       <c r="A1404" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1404" t="n">
-        <v>21776</v>
+        <v>15236</v>
       </c>
       <c r="C1404" t="n">
-        <v>23.5499992370605</v>
+        <v>23.3999996185303</v>
       </c>
       <c r="D1404" t="n">
-        <v>23</v>
+        <v>22.8500003814697</v>
       </c>
       <c r="E1404" t="n">
-        <v>23.1000003814697</v>
+        <v>23.3999996185303</v>
       </c>
       <c r="F1404" t="n">
-        <v>23.1499996185303</v>
+        <v>23.3500003814697</v>
       </c>
       <c r="G1404" t="s">
         <v>7</v>
@@ -32666,22 +32666,22 @@
     </row>
     <row r="1405">
       <c r="A1405" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1405" t="n">
-        <v>20521</v>
+        <v>21776</v>
       </c>
       <c r="C1405" t="n">
-        <v>23.2000007629395</v>
+        <v>23.5499992370605</v>
       </c>
       <c r="D1405" t="n">
-        <v>22.75</v>
+        <v>23</v>
       </c>
       <c r="E1405" t="n">
+        <v>23.1000003814697</v>
+      </c>
+      <c r="F1405" t="n">
         <v>23.1499996185303</v>
-      </c>
-      <c r="F1405" t="n">
-        <v>22.9500007629395</v>
       </c>
       <c r="G1405" t="s">
         <v>7</v>
@@ -32689,22 +32689,22 @@
     </row>
     <row r="1406">
       <c r="A1406" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1406" t="n">
-        <v>13499</v>
+        <v>20521</v>
       </c>
       <c r="C1406" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="E1406" t="n">
         <v>23.1499996185303</v>
       </c>
-      <c r="D1406" t="n">
-        <v>22.7000007629395</v>
-      </c>
-      <c r="E1406" t="n">
-        <v>22.8999996185303</v>
-      </c>
       <c r="F1406" t="n">
-        <v>22.7000007629395</v>
+        <v>22.9500007629395</v>
       </c>
       <c r="G1406" t="s">
         <v>7</v>
@@ -32712,22 +32712,22 @@
     </row>
     <row r="1407">
       <c r="A1407" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1407" t="n">
-        <v>14547</v>
+        <v>13499</v>
       </c>
       <c r="C1407" t="n">
-        <v>23.3999996185303</v>
+        <v>23.1499996185303</v>
       </c>
       <c r="D1407" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="E1407" t="n">
         <v>22.8999996185303</v>
       </c>
-      <c r="E1407" t="n">
-        <v>22.9500007629395</v>
-      </c>
       <c r="F1407" t="n">
-        <v>23.1000003814697</v>
+        <v>22.7000007629395</v>
       </c>
       <c r="G1407" t="s">
         <v>7</v>
@@ -32735,22 +32735,22 @@
     </row>
     <row r="1408">
       <c r="A1408" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1408" t="n">
-        <v>11665</v>
+        <v>14547</v>
       </c>
       <c r="C1408" t="n">
-        <v>23.6000003814697</v>
+        <v>23.3999996185303</v>
       </c>
       <c r="D1408" t="n">
-        <v>23.0499992370605</v>
+        <v>22.8999996185303</v>
       </c>
       <c r="E1408" t="n">
-        <v>23.0499992370605</v>
+        <v>22.9500007629395</v>
       </c>
       <c r="F1408" t="n">
-        <v>23.25</v>
+        <v>23.1000003814697</v>
       </c>
       <c r="G1408" t="s">
         <v>7</v>
@@ -32758,19 +32758,19 @@
     </row>
     <row r="1409">
       <c r="A1409" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1409" t="n">
-        <v>52230</v>
+        <v>11665</v>
       </c>
       <c r="C1409" t="n">
-        <v>23.4500007629395</v>
+        <v>23.6000003814697</v>
       </c>
       <c r="D1409" t="n">
-        <v>22.6000003814697</v>
+        <v>23.0499992370605</v>
       </c>
       <c r="E1409" t="n">
-        <v>23.4500007629395</v>
+        <v>23.0499992370605</v>
       </c>
       <c r="F1409" t="n">
         <v>23.25</v>
@@ -32781,22 +32781,22 @@
     </row>
     <row r="1410">
       <c r="A1410" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1410" t="n">
-        <v>11955</v>
+        <v>52230</v>
       </c>
       <c r="C1410" t="n">
-        <v>23.8500003814697</v>
+        <v>23.4500007629395</v>
       </c>
       <c r="D1410" t="n">
-        <v>23.2999992370605</v>
+        <v>22.6000003814697</v>
       </c>
       <c r="E1410" t="n">
-        <v>23.2999992370605</v>
+        <v>23.4500007629395</v>
       </c>
       <c r="F1410" t="n">
-        <v>23.75</v>
+        <v>23.25</v>
       </c>
       <c r="G1410" t="s">
         <v>7</v>
@@ -32804,24 +32804,47 @@
     </row>
     <row r="1411">
       <c r="A1411" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1411" t="n">
-        <v>17320</v>
+        <v>11955</v>
       </c>
       <c r="C1411" t="n">
-        <v>23.7999992370605</v>
+        <v>23.8500003814697</v>
       </c>
       <c r="D1411" t="n">
         <v>23.2999992370605</v>
       </c>
       <c r="E1411" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="F1411" t="n">
         <v>23.75</v>
       </c>
-      <c r="F1411" t="n">
-        <v>23.3999996185303</v>
-      </c>
       <c r="G1411" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1412" t="n">
+        <v>14533</v>
+      </c>
+      <c r="C1412" t="n">
+        <v>23.5499992370605</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>23</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>23.4500007629395</v>
+      </c>
+      <c r="G1412" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -37139,6 +37139,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1415">
+      <c r="A1415" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1415" t="n">
+        <v>11081</v>
+      </c>
+      <c r="C1415" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>23.5499992370605</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>23.5499992370605</v>
+      </c>
+      <c r="H1415" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -37147,7 +37147,7 @@
         <v>11081</v>
       </c>
       <c r="C1415" t="n">
-        <v>23.5</v>
+        <v>23.5499992370605</v>
       </c>
       <c r="D1415" t="n">
         <v>23.2999992370605</v>
@@ -37162,6 +37162,32 @@
         <v>23.5499992370605</v>
       </c>
       <c r="H1415" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1416" t="n">
+        <v>13075</v>
+      </c>
+      <c r="C1416" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="H1416" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -37191,6 +37191,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1417">
+      <c r="A1417" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1417" t="n">
+        <v>51959</v>
+      </c>
+      <c r="C1417" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="H1417" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -37217,6 +37217,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1418">
+      <c r="A1418" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1418" t="n">
+        <v>25031</v>
+      </c>
+      <c r="C1418" t="n">
+        <v>22.8500003814697</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="H1418" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -37295,6 +37295,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1421">
+      <c r="A1421" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1421" t="n">
+        <v>11879</v>
+      </c>
+      <c r="C1421" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>22.3500003814697</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H1421" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -33117,8 +33117,31 @@
       <c r="E1424" t="n">
         <v>22.2000007629395</v>
       </c>
-      <c r="F1424"/>
+      <c r="F1424" t="n">
+        <v>22.0499992370605</v>
+      </c>
       <c r="G1424" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1425" t="n">
+        <v>13012</v>
+      </c>
+      <c r="C1425" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>22</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="F1425"/>
+      <c r="G1425" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -33140,8 +33140,31 @@
       <c r="E1425" t="n">
         <v>22.6000003814697</v>
       </c>
-      <c r="F1425"/>
+      <c r="F1425" t="n">
+        <v>22.25</v>
+      </c>
       <c r="G1425" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1426" t="n">
+        <v>25475</v>
+      </c>
+      <c r="C1426" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="F1426"/>
+      <c r="G1426" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -33163,8 +33163,31 @@
       <c r="E1426" t="n">
         <v>21.7999992370605</v>
       </c>
-      <c r="F1426"/>
+      <c r="F1426" t="n">
+        <v>22.25</v>
+      </c>
       <c r="G1426" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1427" t="n">
+        <v>20842</v>
+      </c>
+      <c r="C1427" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="F1427"/>
+      <c r="G1427" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -33186,8 +33186,31 @@
       <c r="E1427" t="n">
         <v>22.1000003814697</v>
       </c>
-      <c r="F1427"/>
+      <c r="F1427" t="n">
+        <v>21.8500003814697</v>
+      </c>
       <c r="G1427" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1428" t="n">
+        <v>24654</v>
+      </c>
+      <c r="C1428" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>21.8500003814697</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>21.8500003814697</v>
+      </c>
+      <c r="F1428"/>
+      <c r="G1428" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -33216,6 +33216,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1429">
+      <c r="A1429" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1429" t="n">
+        <v>11749</v>
+      </c>
+      <c r="C1429" t="n">
+        <v>22.0499992370605</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>21.4500007629395</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -37581,6 +37581,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1432">
+      <c r="A1432" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1432" t="n">
+        <v>18198</v>
+      </c>
+      <c r="C1432" t="n">
+        <v>21.6499996185303</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>21.5499992370605</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="H1432" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -37607,6 +37607,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1433">
+      <c r="A1433" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1433" t="n">
+        <v>15214</v>
+      </c>
+      <c r="C1433" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>21.6499996185303</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>21.6499996185303</v>
+      </c>
+      <c r="H1433" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -41935,6 +41935,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1434">
+      <c r="A1434" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1434" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1434" t="n">
+        <v>21.4500007629395</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>21.4500007629395</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>21.0499992370605</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="H1434" t="n">
+        <v>15835</v>
+      </c>
+      <c r="I1434" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1435" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1435" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>21.6499996185303</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>21.6499996185303</v>
+      </c>
+      <c r="H1435" t="n">
+        <v>6273</v>
+      </c>
+      <c r="I1435" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -41975,7 +41975,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="D1435" t="n">
-        <v>21.6000003814697</v>
+        <v>21.6499996185303</v>
       </c>
       <c r="E1435" t="n">
         <v>21</v>
@@ -41990,6 +41990,35 @@
         <v>6273</v>
       </c>
       <c r="I1435" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1436" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1436" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="H1436" t="n">
+        <v>4220</v>
+      </c>
+      <c r="I1436" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -42022,6 +42022,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1437">
+      <c r="A1437" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1437" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1437" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="H1437" t="n">
+        <v>7945</v>
+      </c>
+      <c r="I1437" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -42051,6 +42051,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1438">
+      <c r="A1438" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1438" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1438" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>21.1000003814697</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>21.1000003814697</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>21.1000003814697</v>
+      </c>
+      <c r="H1438" t="n">
+        <v>5324</v>
+      </c>
+      <c r="I1438" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -42080,6 +42080,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1439">
+      <c r="A1439" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1439" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1439" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>21.9500007629395</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="H1439" t="n">
+        <v>15120</v>
+      </c>
+      <c r="I1439" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -42109,6 +42109,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1440">
+      <c r="A1440" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1440" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1440" t="n">
+        <v>21.9500007629395</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>21.9500007629395</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="H1440" t="n">
+        <v>5544</v>
+      </c>
+      <c r="I1440" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -42132,9 +42132,38 @@
         <v>21.25</v>
       </c>
       <c r="H1440" t="n">
-        <v>5544</v>
+        <v>5772</v>
       </c>
       <c r="I1440" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1441" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1441" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1441" t="n">
+        <v>4281</v>
+      </c>
+      <c r="I1441" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -42152,7 +42152,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="E1441" t="n">
-        <v>21.2000007629395</v>
+        <v>21</v>
       </c>
       <c r="F1441" t="n">
         <v>21</v>
@@ -42164,6 +42164,35 @@
         <v>4281</v>
       </c>
       <c r="I1441" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1442" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1442" t="n">
+        <v>21.4500007629395</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>20.9500007629395</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>20.9500007629395</v>
+      </c>
+      <c r="H1442" t="n">
+        <v>5536</v>
+      </c>
+      <c r="I1442" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PHIL.MI.xlsx
+++ b/data/PHIL.MI.xlsx
@@ -42181,7 +42181,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="E1442" t="n">
-        <v>21.1499996185303</v>
+        <v>20.9500007629395</v>
       </c>
       <c r="F1442" t="n">
         <v>20.9500007629395</v>
@@ -42193,6 +42193,35 @@
         <v>5536</v>
       </c>
       <c r="I1442" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1443" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1443" t="n">
+        <v>21.3500003814697</v>
+      </c>
+      <c r="D1443" t="n">
+        <v>21.3500003814697</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="G1443" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="H1443" t="n">
+        <v>5484</v>
+      </c>
+      <c r="I1443" t="s">
         <v>9</v>
       </c>
     </row>
